--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -464,11 +464,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00</t>
+          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Déambule 6 12:00-15:00</t>
+          <t>Déambule Spoutnik 13:00-17:00; Déambule Goulus 19:00-23:00</t>
         </is>
       </c>
     </row>
@@ -494,11 +494,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bar public 19:30-21:00</t>
+          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bar loges 21:00-22:30</t>
+          <t>Déambule FBI 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -524,11 +524,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Déambule 5 19:00-24:00</t>
+          <t>Bourdon.ne 16:00-19:00; Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ailes 18:30-20:30</t>
+          <t>Bourdon.ne 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -554,11 +554,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:30-18:00; Déambule 6 19:00-22:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Déambule 6 19:00-22:00; Entrée backstage 22:30-24:00</t>
+          <t>Entrée backstage 16:00-17:30; Déambule Ko-compagnie 20:00-24:00</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bar public 21:00-22:30</t>
+          <t>Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ailes 20:30-22:30</t>
+          <t>Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -614,11 +614,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bar public 18:00-19:30</t>
+          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -629,13 +629,9 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Entrée backstage 19:30-21:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -644,13 +640,9 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bar public 22:30-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -659,11 +651,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ailes 18:30-20:30</t>
+          <t>Déambule Ko-compagnie 13:00-16:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -678,7 +670,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bar public 19:30-21:00</t>
+          <t>Accueil 16:00-19:00</t>
         </is>
       </c>
     </row>
@@ -689,11 +681,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bar public 22:30-24:00</t>
+          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -704,11 +696,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Déambule 2 13:00-16:00</t>
+          <t>Déambule FBI 12:00-15:00; Déambule Spoutnik 19:00-24:00</t>
         </is>
       </c>
     </row>
@@ -719,11 +711,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Déambule 6 12:00-15:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -738,7 +730,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ailes 22:30-24:00</t>
+          <t>Déambule Goulus 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -749,11 +741,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ailes 16:30-18:30</t>
+          <t>Entrée backstage 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
@@ -764,11 +756,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Déambule 1 13:00-15:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -783,7 +775,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Entrée backstage 17:30-19:00</t>
         </is>
       </c>
     </row>
@@ -798,7 +790,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ailes 22:30-24:00</t>
+          <t>Tech Muchmuche 18:00-20:00</t>
         </is>
       </c>
     </row>
@@ -813,7 +805,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bar loges 21:00-22:30</t>
+          <t>Bourdon.ne 16:00-19:00</t>
         </is>
       </c>
     </row>
@@ -824,11 +816,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bar public 16:30-18:00</t>
+          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -839,11 +831,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ailes 16:30-18:30</t>
+          <t>Déambule Colbok 13:00-16:00; Tech PCGB 19:00-21:00</t>
         </is>
       </c>
     </row>
@@ -858,7 +850,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ailes 22:30-24:00</t>
+          <t>Bar loges 18:00-19:30</t>
         </is>
       </c>
     </row>
@@ -869,11 +861,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bar public 18:00-19:30</t>
+          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -888,7 +880,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bar public 22:30-24:00</t>
+          <t>Ailes 18:00-20:00</t>
         </is>
       </c>
     </row>
@@ -903,7 +895,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Déambule 4 20:00-24:00</t>
+          <t>Déambule Goulus 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -914,11 +906,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00</t>
+          <t>Tech T'es rien… 17:00-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -929,11 +921,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tech Jacquard 22:00-23:30</t>
+          <t>Bar loges 19:30-21:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -944,11 +936,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bar loges 22:30-24:00</t>
+          <t>Abeilles Ruche 17:30-19:00; Entrée backstage 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -963,7 +955,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Déambule 3 19:00-23:00</t>
+          <t>Déambule Colbok 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -974,11 +966,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bar public 18:00-19:30</t>
+          <t>Bar loges 18:00-19:30; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -989,11 +981,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ailes 16:30-18:30</t>
+          <t>Ailes 18:00-20:00; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1000,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tech Muchmuche 19:00-21:00</t>
+          <t>Entrée backstage 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1015,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ailes 20:30-22:30</t>
+          <t>Accueil 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -1034,11 +1026,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Déambule 3 19:00-23:00</t>
+          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1049,11 +1041,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Déambule 3 19:00-22:00</t>
+          <t>Déambule Gerry 13:00-15:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1064,11 +1056,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tech T'es rien… 18:30-19:30</t>
+          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1075,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30</t>
+          <t>Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1094,11 +1086,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1109,11 +1101,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ailes 18:30-20:30</t>
+          <t>Ailes 18:00-20:00; Bourdon.ne 22:00-00:30</t>
         </is>
       </c>
     </row>
@@ -1124,11 +1116,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Entrée backstage 21:00-22:30</t>
+          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -1139,11 +1131,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Déambule 5 13:00-17:00</t>
+          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1150,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Déambule 4 13:00-16:00; Entrée backstage 18:00-19:30</t>
+          <t>Bar public 16:00-17:30; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1169,11 +1161,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bar loges 22:30-24:00</t>
+          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1180,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Déambule 3 19:00-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bar public 19:30-21:00</t>
+          <t>Bar public 16:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1214,11 +1206,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bar public 16:30-18:00</t>
+          <t>Ailes 16:00-18:00; Bourdon.ne 22:00-00:30</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1225,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bar public 19:30-21:00</t>
+          <t>Bourdon.ne 19:00-22:00</t>
         </is>
       </c>
     </row>
@@ -1244,11 +1236,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ailes 20:30-22:30</t>
+          <t>Abeilles Ruche 16:00-17:30; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1259,11 +1251,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -1274,11 +1266,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bar public 21:00-22:30</t>
+          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1285,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bar public 21:00-22:30</t>
+          <t>Déambule Goulus 19:00-23:00</t>
         </is>
       </c>
     </row>
@@ -1304,13 +1296,9 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tech PCGB 17:00-18:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1323,7 +1311,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bar public 16:30-18:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Déambule 2 19:00-22:00</t>
+          <t>Déambule Gerry 19:00-23:00</t>
         </is>
       </c>
     </row>
@@ -1349,11 +1337,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Déambule 1 19:00-23:00</t>
+          <t>Abeilles Ruche 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1356,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bar public 21:00-22:30</t>
+          <t>Bar public 16:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1435,17 +1423,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1459,24 +1447,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agathe Bouvet</t>
+          <t>Julie Chavaillaz</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1490,117 +1478,117 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ysatis Ménétrey</t>
+          <t>Lisa Magnin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Maëlle Chambaz</t>
+          <t>Louis Post, Theo Cyprien, Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey</t>
+          <t>Corentin Meige, Eugénie Prouvost, Roxanne Lanni</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka</t>
+          <t>Antonin Noël, Arthur Uldry, Léa Baltzinger</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1614,24 +1602,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Marius Felix, Marot Ledru, Mathis Cuinet</t>
+          <t>Enzo Maître, Lisa Jaquet, Louis Cardis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1645,38 +1633,38 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Louise Blanchard, Lucas Chastroux, Lucie Meyer</t>
+          <t>Léa Chambaz, Lina-Rosa Ledru, Theo Cyprien</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lisa Magnin, Louis Cardis, Louis Post</t>
+          <t>Arthur Uldry, Marot Ledru</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1676,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1707,24 +1695,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Matteo Gavin, Maxime Debray, Maya Corbelli</t>
+          <t>Iris Rakotonandrasana, Mickaël Pasche, Raphaëlle Neidhart</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1738,24 +1726,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mickaël Pasche, Morgana Fargues, Morgane Scyboz (Lambelet)</t>
+          <t>Lucie Meyer, Marot Ledru, Nathalia Koux</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1769,100 +1757,100 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Lina-Rosa Ledru, Lisa Jaquet</t>
+          <t>Lucas Chastroux, Maëlan Ménétrey, Rama Assaoui</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jules Pirolley, Julie Chavaillaz, Kristel Oeschger, Léa Baltzinger</t>
+          <t>Corentin Meige, Louis Post, Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana, Jamilah Bürgisser, Jolan Ruscio, Jonas Wuilloud</t>
+          <t>Maëlan Ménétrey, Rama Assaoui</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nathalia Koux, Noah Cherpillod, Patrick Chambaz</t>
+          <t>Lina-Rosa Ledru, Matteo Gavin</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1862,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1893,7 +1881,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rama Assaoui, Raphaël Lacroze</t>
+          <t>Jamilah Bürgisser, Simon Lambelet</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1893,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1924,7 +1912,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Enzo Maître, Eugénie Prouvost</t>
+          <t>Alexandra Bastian, Noah Cherpillod</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1924,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1955,212 +1943,212 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corentin Meige, Emma De Filippo</t>
+          <t>Mathis Cuinet, Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ava Baruch, Benoît Detrain</t>
+          <t>Anna Mallet, Lisa Jaquet, Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Raphaëlle Neidhart, Roxanne Lanni</t>
+          <t>Athénaé Marchand, Léa Chambaz, Noah Cherpillod</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tech PCGB</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sébastien Schiesser</t>
+          <t>Agathe Bouvet, Morgana Fargues, Morgane Scyboz (Lambelet), Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tech Jacquard</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Simon Lambelet</t>
+          <t>Anna Mallet, Annouk Malric, Iris Rakotonandrasana, Raphaëlle Neidhart</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tech Muchmuche</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Athénaé Marchand, Raphaël Lacroze, Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tech T'es rien…</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Athénaé Marchand</t>
+          <t>Eugénie Prouvost, Morgana Fargues, Simon Lambelet</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Déambule 1</t>
+          <t>Bourdon.ne</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
@@ -2172,24 +2160,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthur Uldry</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Déambule 1</t>
+          <t>Bourdon.ne</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2203,24 +2191,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Theo Cyprien</t>
+          <t>Jules Pirolley</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Déambule 2</t>
+          <t>Bourdon.ne</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2234,24 +2222,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arsène Tessier</t>
+          <t>Mickaël Pasche</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Déambule 2</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2265,45 +2253,45 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Alegria Lily Bulka</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Déambule 3</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Annouk Malric, Antonin Noël</t>
+          <t>Emma De Filippo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Déambule 3</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2313,38 +2301,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Analou Ledru, Anna Mallet</t>
+          <t>Mathis Cuinet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Déambule 4</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2358,24 +2346,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ysatis Ménétrey</t>
+          <t>Auxence Magerand</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Déambule 4</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2389,24 +2377,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Roxanne Lanni</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Déambule 5</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2420,14 +2408,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Léa Baltzinger</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Déambule 5</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2437,7 +2425,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2451,19 +2439,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Arsène Tessier</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Déambule 6</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2472,24 +2460,24 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tristan Clerici, Yann Bally</t>
+          <t>Annouk Malric</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Déambule 6</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2503,22 +2491,549 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Agathe Bouvet, Alegria Lily Bulka</t>
+          <t>Analou Ledru</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Déambule Colbok</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Marius Felix</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Déambule Goulus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alice L'Horset, Maya Corbelli</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Déambule Goulus</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Jolan Ruscio, Yann Bally</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Déambule Ko-compagnie</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lucas Chastroux</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Déambule Ko-compagnie</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alegria Lily Bulka</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Déambule Spoutnik</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yann Bally</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Déambule Spoutnik</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thibault Clerici</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Déambule FBI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thibault Clerici</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Déambule FBI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ava Baruch</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Bourdon.ne</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Benoît Detrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bar public</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Jonas Wuilloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bar public</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Kristel Oeschger</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bourdon.ne</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Louise Blanchard</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Bourdon.ne</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lucie Meyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tech PCGB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Marius Felix</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tech Muchmuche</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Maxime Debray</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tech T'es rien…</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Raphaël Lacroze</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>

--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,37 +460,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rama Assaoui</t>
+          <t>Agathe Bouvet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
+          <t>Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yann Bally</t>
+          <t>Alegria Lily Bulka</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik 13:00-17:00; Déambule Goulus 19:00-23:00</t>
+          <t>Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Léa Baltzinger</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -498,74 +498,74 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
+          <t>Déambule Spoutnik 17:00-19:00; Déambule Spoutnik 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ava Baruch</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Déambule FBI 19:00-22:00</t>
+          <t>Entrée backstage 17:30-19:00; Entrée backstage 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Analou Ledru</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bourdon.ne 16:00-19:00; Bar loges 21:00-22:30</t>
+          <t>Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Louise Blanchard</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bourdon.ne 19:00-22:00</t>
+          <t>Déambule Ko-compagnie 16:30-18:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agathe Bouvet</t>
+          <t>Annouk Malric</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Déambule Goulus 16:30-18:00; Déambule Ko-compagnie 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka</t>
+          <t>Antonin Noël</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:00-17:30; Déambule Ko-compagnie 20:00-24:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamilah Bürgisser</t>
+          <t>Arsène Tessier</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -588,29 +588,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Louis Cardis</t>
+          <t>Arthur Uldry</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 20:30-22:00</t>
+          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Léa Chambaz</t>
+          <t>Athénaé Marchand</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -618,66 +618,70 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Déambule Goulus 16:30-18:00; Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maëlle Chambaz</t>
+          <t>Auxence Magerand</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Déambule Gerry 16:30-18:00; Entrée backstage 20:30-22:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Patrick Chambaz</t>
+          <t>Ava Baruch</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Déambule Colbok 21:00-23:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lucas Chastroux</t>
+          <t>Benoît Detrain</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Déambule Ko-compagnie 13:00-16:00; Ailes 20:00-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Julie Chavaillaz</t>
+          <t>Corentin Meige</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accueil 16:00-19:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Déambule Gerry 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Noah Cherpillod</t>
+          <t>Emma De Filippo</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -685,14 +689,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
+          <t>Ailes 16:00-18:00; Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Enzo Maître</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -700,14 +704,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Déambule FBI 12:00-15:00; Déambule Spoutnik 19:00-24:00</t>
+          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tristan Clerici</t>
+          <t>Eugénie Prouvost</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -715,44 +719,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
+          <t>Bar loges 18:00-19:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maya Corbelli</t>
+          <t>Iris Rakotonandrasana</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Déambule Goulus 19:00-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mathis Cuinet</t>
+          <t>Jamilah Bürgisser</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Entrée backstage 19:00-20:30; Bar loges 22:30-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Theo Cyprien</t>
+          <t>Jolan Ruscio</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -760,29 +760,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Emma De Filippo</t>
+          <t>Jonas Wuilloud</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Entrée backstage 17:30-19:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maxime Debray</t>
+          <t>Jules Pirolley</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -790,59 +786,51 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tech Muchmuche 18:00-20:00</t>
+          <t>Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Benoît Detrain</t>
+          <t>Julie Chavaillaz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Bourdon.ne 16:00-19:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Morgana Fargues</t>
+          <t>Kristel Oeschger</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marius Felix</t>
+          <t>Lina-Rosa Ledru</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Déambule Colbok 13:00-16:00; Tech PCGB 19:00-21:00</t>
+          <t>Abeilles Ruche 17:30-19:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matteo Gavin</t>
+          <t>Lisa Jaquet</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -850,74 +838,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30</t>
+          <t>Bar loges 16:30-18:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lisa Jaquet</t>
+          <t>Lisa Magnin</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nathalia Koux</t>
+          <t>Louis Cardis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00</t>
+          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Louis Post</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Déambule Goulus 19:00-22:00</t>
+          <t>Ailes 18:00-20:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Raphaël Lacroze</t>
+          <t>Louise Blanchard</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tech T'es rien… 17:00-19:00; Bar public 22:00-23:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Simon Lambelet</t>
+          <t>Lucas Chastroux</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -925,14 +905,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00; Bar public 23:30-00:30</t>
+          <t>Bar loges 16:30-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Roxanne Lanni</t>
+          <t>Lucie Meyer</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -940,14 +920,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Entrée backstage 22:00-23:30</t>
+          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analou Ledru</t>
+          <t>Léa Baltzinger</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -955,14 +935,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Déambule Colbok 19:00-22:00</t>
+          <t>Abeilles Ruche 17:30-19:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lina-Rosa Ledru</t>
+          <t>Léa Chambaz</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -970,134 +950,118 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30; Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marot Ledru</t>
+          <t>Marius Felix</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ailes 18:00-20:00; Abeilles Ruche 23:30-00:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Marot Ledru</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Entrée backstage 20:30-22:00</t>
+          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lisa Magnin</t>
+          <t>Mathis Cuinet</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Accueil 19:00-22:00</t>
+          <t>Bar public 17:30-19:00; Tech Jacquard 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anna Mallet</t>
+          <t>Matteo Gavin</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Annouk Malric</t>
+          <t>Maxime Debray</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Déambule Gerry 13:00-15:00; Bar public 20:30-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Athénaé Marchand</t>
+          <t>Maya Corbelli</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enzo Maître</t>
+          <t>Maëlan Ménétrey</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 20:30-22:00</t>
+          <t>Entrée backstage 16:00-17:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Corentin Meige</t>
+          <t>Maëlle Chambaz</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lucie Meyer</t>
+          <t>Mickaël Pasche</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1105,14 +1069,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Bourdon.ne 22:00-00:30</t>
+          <t>Bar loges 18:00-19:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey</t>
+          <t>Mireille Ménard</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1120,14 +1084,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
+          <t>Tech Muchmuche 19:00-21:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Morgana Fargues</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1135,14 +1099,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
+          <t>Tech PCGB 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ysatis Ménétrey</t>
+          <t>Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1150,29 +1114,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Ailes 22:00-24:00</t>
+          <t>Bar public 16:00-17:30; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Raphaëlle Neidhart</t>
+          <t>Nathalia Koux</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Antonin Noël</t>
+          <t>Noah Cherpillod</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1180,29 +1144,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kristel Oeschger</t>
+          <t>Patrick Chambaz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Bar public 16:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mickaël Pasche</t>
+          <t>Rama Assaoui</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1210,14 +1170,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Bourdon.ne 22:00-00:30</t>
+          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jules Pirolley</t>
+          <t>Raphaël Lacroze</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1225,29 +1185,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bourdon.ne 19:00-22:00</t>
+          <t>Tech T'es rien… 17:00-19:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Louis Post</t>
+          <t>Raphaëlle Neidhart</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Ailes 22:00-24:00</t>
+          <t>Déambule FBI 17:00-19:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Eugénie Prouvost</t>
+          <t>Roxanne Lanni</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1255,14 +1215,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
+          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana</t>
+          <t>Simon Lambelet</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1270,93 +1230,108 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
+          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jolan Ruscio</t>
+          <t>Sébastien Schiesser</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Déambule Goulus 19:00-23:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sébastien Schiesser</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Morgane Scyboz (Lambelet)</t>
+          <t>Thibault Clerici</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Arsène Tessier</t>
+          <t>Titouan Ménétrey</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Déambule Gerry 19:00-23:00</t>
+          <t>Déambule Colbok 17:00-19:00; Déambule FBI 21:30-23:30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Arthur Uldry</t>
+          <t>Tristan Clerici</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
+          <t>Entrée backstage 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jonas Wuilloud</t>
+          <t>Yann Bally</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bar public 16:00-24:00</t>
+          <t>Bar loges 19:30-21:00; Abeilles Ruche 23:30-00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ysatis Ménétrey</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Abeilles Ruche 16:00-17:30; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1423,7 +1398,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1433,52 +1408,52 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Julie Chavaillaz</t>
+          <t>Antonin Noël, Corentin Meige, Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lisa Magnin</t>
+          <t>Léa Baltzinger, Lina-Rosa Ledru, Thibault Clerici</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1465,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1509,7 +1484,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Louis Post, Theo Cyprien, Tristan Clerici</t>
+          <t>Iris Rakotonandrasana, Maya Corbelli, Nathalia Koux</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1496,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1540,7 +1515,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corentin Meige, Eugénie Prouvost, Roxanne Lanni</t>
+          <t>Morgana Fargues, Rama Assaoui, Simon Lambelet</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1527,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1571,7 +1546,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antonin Noël, Arthur Uldry, Léa Baltzinger</t>
+          <t>Alegria Lily Bulka, Arthur Uldry, Louis Post</t>
         </is>
       </c>
     </row>
@@ -1583,43 +1558,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Enzo Maître, Lisa Jaquet, Louis Cardis</t>
+          <t>Mickaël Pasche, Yann Bally</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Abeilles Ruche</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1633,38 +1608,38 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Lina-Rosa Ledru, Theo Cyprien</t>
+          <t>Emma De Filippo, Rama Assaoui, Simon Lambelet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Abeilles Ruche</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthur Uldry, Marot Ledru</t>
+          <t>Louis Post, Marot Ledru, Roxanne Lanni</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1651,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1695,7 +1670,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana, Mickaël Pasche, Raphaëlle Neidhart</t>
+          <t>Antonin Noël, Arsène Tessier, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1682,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1726,69 +1701,69 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lucie Meyer, Marot Ledru, Nathalia Koux</t>
+          <t>Marot Ledru, Roxanne Lanni, Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lucas Chastroux, Maëlan Ménétrey, Rama Assaoui</t>
+          <t>Lisa Jaquet, Lucas Chastroux</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corentin Meige, Louis Post, Ysatis Ménétrey</t>
+          <t>Eugénie Prouvost, Mickaël Pasche</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1775,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1819,7 +1794,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey, Rama Assaoui</t>
+          <t>Jules Pirolley, Yann Bally</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1806,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1850,7 +1825,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lina-Rosa Ledru, Matteo Gavin</t>
+          <t>Analou Ledru, Theo Cyprien</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1837,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1881,69 +1856,69 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jamilah Bürgisser, Simon Lambelet</t>
+          <t>Léa Chambaz, Louis Cardis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alexandra Bastian, Noah Cherpillod</t>
+          <t>Enzo Maître, Jolan Ruscio, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mathis Cuinet, Titouan Ménétrey</t>
+          <t>Arthur Uldry, Mathis Cuinet, Theo Cyprien</t>
         </is>
       </c>
     </row>
@@ -1955,26 +1930,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anna Mallet, Lisa Jaquet, Ysatis Ménétrey</t>
+          <t>Léa Chambaz, Louis Cardis, Lucie Meyer, Noah Cherpillod</t>
         </is>
       </c>
     </row>
@@ -1986,26 +1961,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Athénaé Marchand, Léa Chambaz, Noah Cherpillod</t>
+          <t>Agathe Bouvet, Enzo Maître, Jolan Ruscio, Lucas Chastroux</t>
         </is>
       </c>
     </row>
@@ -2017,26 +1992,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Agathe Bouvet, Morgana Fargues, Morgane Scyboz (Lambelet), Titouan Ménétrey</t>
+          <t>Anna Mallet, Eugénie Prouvost, Thibault Clerici</t>
         </is>
       </c>
     </row>
@@ -2048,105 +2023,105 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anna Mallet, Annouk Malric, Iris Rakotonandrasana, Raphaëlle Neidhart</t>
+          <t>Lucie Meyer, Maëlan Ménétrey, Mireille Ménard</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Athénaé Marchand, Raphaël Lacroze, Tristan Clerici</t>
+          <t>Maëlan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eugénie Prouvost, Morgana Fargues, Simon Lambelet</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bourdon.ne</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2160,19 +2135,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bourdon.ne</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2191,14 +2166,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jules Pirolley</t>
+          <t>Auxence Magerand</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bourdon.ne</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2208,7 +2183,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2222,7 +2197,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mickaël Pasche</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2209,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2253,24 +2228,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka</t>
+          <t>Iris Rakotonandrasana</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2284,24 +2259,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emma De Filippo</t>
+          <t>Auxence Magerand</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2315,24 +2290,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mathis Cuinet</t>
+          <t>Corentin Meige</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2346,24 +2321,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2377,86 +2352,86 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Roxanne Lanni</t>
+          <t>Ava Baruch</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Déambule Goulus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Léa Baltzinger</t>
+          <t>Annouk Malric, Athénaé Marchand</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Déambule Gerry</t>
+          <t>Déambule Goulus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arsène Tessier</t>
+          <t>Athénaé Marchand, Emma De Filippo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Déambule Gerry</t>
+          <t>Déambule Ko-compagnie</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2470,19 +2445,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Annouk Malric</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Déambule Colbok</t>
+          <t>Déambule Ko-compagnie</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2501,24 +2476,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Analou Ledru</t>
+          <t>Annouk Malric</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Déambule Colbok</t>
+          <t>Déambule Spoutnik</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2532,86 +2507,86 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Marius Felix</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Déambule Goulus</t>
+          <t>Déambule Spoutnik</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alice L'Horset, Maya Corbelli</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Déambule Goulus</t>
+          <t>Déambule FBI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jolan Ruscio, Yann Bally</t>
+          <t>Raphaëlle Neidhart</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie</t>
+          <t>Déambule FBI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2625,24 +2600,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lucas Chastroux</t>
+          <t>Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie</t>
+          <t>Tech Jacquard</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2656,24 +2631,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka</t>
+          <t>Mathis Cuinet</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik</t>
+          <t>Tech PCGB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2687,26 +2662,26 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yann Bally</t>
+          <t>Morgana Fargues</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik</t>
+          <t>Tech T'es rien…</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
@@ -2718,24 +2693,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Raphaël Lacroze</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Déambule FBI</t>
+          <t>Tech Muchmuche</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2749,291 +2724,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Mireille Ménard</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Déambule FBI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Ava Baruch</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>(**) Personne affectée malgré un blocage de priorité 1</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bourdon.ne</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Benoît Detrain</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Bar public</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Jonas Wuilloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Bar public</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Kristel Oeschger</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Bourdon.ne</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Louise Blanchard</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Bourdon.ne</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Lucie Meyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tech PCGB</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Marius Felix</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tech Muchmuche</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Maxime Debray</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Tech T'es rien…</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Raphaël Lacroze</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -3099,7 +2802,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tous les besoins sont couverts et toutes les préférences respectées</t>
+          <t>Tous les besoins sont couverts et tous les blocages respectés</t>
         </is>
       </c>
     </row>

--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar public 20:30-22:00</t>
+          <t>Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik 17:00-19:00; Déambule Spoutnik 21:00-23:00</t>
+          <t>Abeilles Ruche 17:30-19:00; Déambule FBI 21:30-23:30</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Entrée backstage 17:30-19:00; Entrée backstage 22:00-23:30</t>
+          <t>Ailes 16:00-18:00; Déambule Spoutnik 21:00-23:00</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bar loges 21:00-22:30</t>
+          <t>Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie 16:30-18:30; Bar public 22:00-23:30</t>
+          <t>Bar loges 18:00-19:30; Entrée backstage 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Déambule Ko-compagnie 20:00-22:00</t>
+          <t>Entrée backstage 16:00-17:30; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Ailes 20:00-22:00</t>
+          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ailes 20:00-22:00</t>
+          <t>Déambule Gerry 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Déambule Goulus 16:30-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Déambule Goulus 20:00-21:30</t>
+          <t>Abeilles Ruche 16:00-17:30; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Déambule Gerry 16:30-18:00; Entrée backstage 20:30-22:00</t>
+          <t>Déambule Goulus 16:30-18:00; Entrée backstage 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Déambule Gerry 20:30-22:00</t>
+          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -685,11 +685,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Déambule Goulus 20:00-21:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30; Bar public 22:00-23:30</t>
+          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
+          <t>Ailes 16:00-18:00; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Abeilles Ruche 17:30-19:00</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00</t>
+          <t>Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
+          <t>Ailes 18:00-20:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Bar public 20:30-22:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Déambule Ko-compagnie 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
+          <t>Déambule Spoutnik 17:00-19:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
+          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
+          <t>Déambule Goulus 20:00-21:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Tech Jacquard 21:00-23:00</t>
+          <t>Entrée backstage 17:30-19:00; Tech Jacquard 21:00-23:00</t>
         </is>
       </c>
     </row>
@@ -1028,14 +1028,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Déambule Ko-compagnie 16:30-18:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey</t>
+          <t>Maya Rieger</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1043,55 +1043,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:00-17:30; Bar public 23:30-00:30</t>
+          <t>Déambule FBI 17:00-19:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maëlle Chambaz</t>
+          <t>Maëlan Ménétrey</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bar public 17:30-19:00; Bar loges 22:30-24:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mickaël Pasche</t>
+          <t>Maëlle Chambaz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Bar loges 18:00-19:30; Abeilles Ruche 23:30-00:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mireille Ménard</t>
+          <t>Mickaël Pasche</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tech Muchmuche 19:00-21:00; Bar public 23:30-00:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Morgana Fargues</t>
+          <t>Mireille Ménard</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tech PCGB 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Tech Muchmuche 19:00-21:00; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Morgane Scyboz (Lambelet)</t>
+          <t>Morgana Fargues</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1114,29 +1114,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Ailes 20:00-22:00</t>
+          <t>Tech PCGB 16:00-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nathalia Koux</t>
+          <t>Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Noah Cherpillod</t>
+          <t>Nathalia Koux</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1144,55 +1144,55 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Entrée backstage 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Patrick Chambaz</t>
+          <t>Noah Cherpillod</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ailes 16:00-18:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Rama Assaoui</t>
+          <t>Patrick Chambaz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Raphaël Lacroze</t>
+          <t>Rama Assaoui</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tech T'es rien… 17:00-19:00</t>
+          <t>Bar loges 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Raphaëlle Neidhart</t>
+          <t>Raphaël Lacroze</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1200,29 +1200,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Déambule FBI 17:00-19:00</t>
+          <t>Tech T'es rien… 17:00-19:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Roxanne Lanni</t>
+          <t>Raphaëlle Neidhart</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Simon Lambelet</t>
+          <t>Roxanne Lanni</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1230,40 +1230,40 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sébastien Schiesser</t>
+          <t>Simon Lambelet</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bar loges 18:00-19:30; Ailes 22:00-24:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Theo Cyprien</t>
+          <t>Sébastien Schiesser</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1271,14 +1271,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Bar public 22:00-23:30</t>
+          <t>Déambule Gerry 16:30-18:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Thibault Clerici</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1286,52 +1286,67 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Déambule Colbok 17:00-19:00; Déambule FBI 21:30-23:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tristan Clerici</t>
+          <t>Titouan Ménétrey</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Entrée backstage 19:00-20:30</t>
+          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Yann Bally</t>
+          <t>Tristan Clerici</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00; Abeilles Ruche 23:30-00:30</t>
+          <t>Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Yann Bally</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Ysatis Ménétrey</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 16:00-17:30; Ailes 22:00-24:00</t>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Déambule Colbok 17:00-19:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1437,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antonin Noël, Corentin Meige, Ysatis Ménétrey</t>
+          <t>Athénaé Marchand, Lucas Chastroux, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1468,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Léa Baltzinger, Lina-Rosa Ledru, Thibault Clerici</t>
+          <t>Alexandra Bastian, Jules Pirolley, Thibault Clerici</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1499,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana, Maya Corbelli, Nathalia Koux</t>
+          <t>Emma De Filippo, Léa Baltzinger, Mickaël Pasche</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1530,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Morgana Fargues, Rama Assaoui, Simon Lambelet</t>
+          <t>Corentin Meige, Rama Assaoui, Titouan Ménétrey</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1561,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka, Arthur Uldry, Louis Post</t>
+          <t>Jolan Ruscio, Theo Cyprien, Thibault Clerici</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1592,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mickaël Pasche, Yann Bally</t>
+          <t>Léa Chambaz, Marot Ledru</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1623,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emma De Filippo, Rama Assaoui, Simon Lambelet</t>
+          <t>Alice L'Horset, Iris Rakotonandrasana, Noah Cherpillod</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1654,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Louis Post, Marot Ledru, Roxanne Lanni</t>
+          <t>Antonin Noël, Louis Cardis, Louis Post</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1685,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antonin Noël, Arsène Tessier, Morgane Scyboz (Lambelet)</t>
+          <t>Annouk Malric, Athénaé Marchand, Enzo Maître</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1716,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marot Ledru, Roxanne Lanni, Ysatis Ménétrey</t>
+          <t>Simon Lambelet, Ysatis Ménétrey, Maya Rieger</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1747,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lisa Jaquet, Lucas Chastroux</t>
+          <t>Enzo Maître, Rama Assaoui</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1778,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eugénie Prouvost, Mickaël Pasche</t>
+          <t>Anna Mallet, Simon Lambelet</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1809,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jules Pirolley, Yann Bally</t>
+          <t>Lisa Jaquet, Tristan Clerici</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1840,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Analou Ledru, Theo Cyprien</t>
+          <t>Agathe Bouvet, Eugénie Prouvost</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1871,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Louis Cardis</t>
+          <t>Iris Rakotonandrasana, Maëlan Ménétrey</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Enzo Maître, Jolan Ruscio, Morgane Scyboz (Lambelet)</t>
+          <t>Corentin Meige, Roxanne Lanni, Titouan Ménétrey</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1933,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthur Uldry, Mathis Cuinet, Theo Cyprien</t>
+          <t>Eugénie Prouvost, Jolan Ruscio, Maëlan Ménétrey</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1964,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Louis Cardis, Lucie Meyer, Noah Cherpillod</t>
+          <t>Léa Chambaz, Lina-Rosa Ledru, Raphaëlle Neidhart, Yann Bally</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1995,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agathe Bouvet, Enzo Maître, Jolan Ruscio, Lucas Chastroux</t>
+          <t>Alegria Lily Bulka, Arthur Uldry, Morgana Fargues, Roxanne Lanni</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2026,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anna Mallet, Eugénie Prouvost, Thibault Clerici</t>
+          <t>Antonin Noël, Louis Post, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2057,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lucie Meyer, Maëlan Ménétrey, Mireille Ménard</t>
+          <t>Louis Cardis, Lucie Meyer, Yann Bally</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2088,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey</t>
+          <t>Annouk Malric</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2119,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Mathis Cuinet</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2150,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tristan Clerici</t>
+          <t>Nathalia Koux</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2212,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2243,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana</t>
+          <t>Mireille Ménard</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2274,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2305,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corentin Meige</t>
+          <t>Arsène Tessier</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2336,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2398,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Annouk Malric, Athénaé Marchand</t>
+          <t>Arthur Uldry, Auxence Magerand</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2429,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Athénaé Marchand, Emma De Filippo</t>
+          <t>Analou Ledru, Marot Ledru</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2460,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anna Mallet</t>
+          <t>Maya Corbelli</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2491,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Annouk Malric</t>
+          <t>Lucas Chastroux</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2522,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Lucie Meyer</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2553,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2584,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Raphaëlle Neidhart</t>
+          <t>Maya Rieger</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2615,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
     </row>

--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agathe Bouvet</t>
+          <t>Agathe</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -468,14 +468,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar loges 21:00-22:30</t>
+          <t>Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka</t>
+          <t>Alegria Lily</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,14 +483,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bar public 20:30-22:00</t>
+          <t>Déambule Gerry 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -498,14 +498,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Déambule FBI 21:30-23:30</t>
+          <t>Déambule Spoutnik 17:00-19:00; Déambule Spoutnik 22:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -513,14 +513,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Déambule Spoutnik 21:00-23:00</t>
+          <t>Bar public 16:00-17:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analou Ledru</t>
+          <t>Analou</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -528,14 +528,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Déambule Goulus 20:00-21:30</t>
+          <t>Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anna Mallet</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -543,14 +543,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30; Entrée backstage 22:00-23:30</t>
+          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Annouk Malric</t>
+          <t>Annouk</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -558,14 +558,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:00-17:30; Ailes 20:00-22:00</t>
+          <t>Entrée backstage 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antonin Noël</t>
+          <t>Antonin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -573,14 +573,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
+          <t>Bar public 17:30-19:00; Entrée backstage 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arsène Tessier</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -588,14 +588,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Déambule Gerry 20:30-22:00</t>
+          <t>Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Arthur Uldry</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -603,14 +603,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Bar public 20:30-22:00</t>
+          <t>Déambule Gerry 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Athénaé Marchand</t>
+          <t>Athénaé</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -618,29 +618,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Ailes 20:00-22:00</t>
+          <t>Bar public 16:00-17:30; Entrée backstage 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Auxence</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Entrée backstage 20:30-22:00</t>
+          <t>Entrée backstage 17:30-19:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ava Baruch</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -655,7 +655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Benoît Detrain</t>
+          <t>Benoît</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -666,7 +666,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Corentin Meige</t>
+          <t>Corentin</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Emma De Filippo</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Déambule Volkanik 16:30-18:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enzo Maître</t>
+          <t>Enzo</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -704,29 +704,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Ailes 20:00-22:00</t>
+          <t>Ailes 16:00-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Eugénie Prouvost</t>
+          <t>Eugénie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana</t>
+          <t>Iris</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -734,14 +730,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Bar loges 22:30-24:00</t>
+          <t>Bar public 19:00-20:30; Déambule Volkanik 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamilah Bürgisser</t>
+          <t>Jamilah</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -752,7 +748,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jolan Ruscio</t>
+          <t>Jolan</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -760,14 +756,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jonas Wuilloud</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -778,7 +774,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jules Pirolley</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -786,14 +782,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00</t>
+          <t>Entrée backstage 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julie Chavaillaz</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -804,7 +800,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kristel Oeschger</t>
+          <t>Kristel</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -815,22 +811,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lina-Rosa Ledru</t>
+          <t>Lina-Rosa</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Bar public 16:00-17:30; Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lisa Jaquet</t>
+          <t>Lisa J.</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -838,14 +834,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Bar loges 18:00-19:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lisa Magnin</t>
+          <t>Lisa M.</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -856,7 +852,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Louis Cardis</t>
+          <t>Louis C.</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -864,14 +860,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Bar public 23:30-00:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Louis Post</t>
+          <t>Louis P.</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -879,14 +875,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
+          <t>Bar loges 16:30-18:00; Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Louise Blanchard</t>
+          <t>Louise</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -897,7 +893,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lucas Chastroux</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -905,14 +901,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Déambule Ko-compagnie 20:00-22:00</t>
+          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lucie Meyer</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -920,14 +916,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik 17:00-19:00; Bar public 23:30-00:30</t>
+          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Léa Baltzinger</t>
+          <t>Léa B.</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -935,14 +931,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Ailes 18:00-20:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Léa Chambaz</t>
+          <t>Léa C.</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -950,14 +946,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
+          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marius Felix</t>
+          <t>Marius</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -968,7 +964,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marot Ledru</t>
+          <t>Marot</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -976,14 +972,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Déambule Goulus 20:00-21:30; Abeilles Ruche 23:30-00:30</t>
+          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mathis Cuinet</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -991,14 +987,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entrée backstage 17:30-19:00; Tech Jacquard 21:00-23:00</t>
+          <t>Déambule FBI 17:00-19:00; Tech Jacquard 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Matteo Gavin</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1009,7 +1005,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maxime Debray</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1020,7 +1016,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maya Corbelli</t>
+          <t>Maya C.</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1028,29 +1024,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie 16:30-18:30</t>
+          <t>Abeilles Ruche 17:30-19:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maya Rieger</t>
+          <t>Maya R.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Déambule FBI 17:00-19:00; Ailes 22:00-24:00</t>
+          <t>Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maëlan Ménétrey</t>
+          <t>Maëlan</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1058,14 +1054,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar loges 22:30-24:00</t>
+          <t>Déambule Colbok 17:00-19:00; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maëlle Chambaz</t>
+          <t>Maëlle</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1076,22 +1072,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mickaël Pasche</t>
+          <t>Mickaël</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Bar loges 19:30-21:00; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mireille Ménard</t>
+          <t>Mireille</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1099,14 +1095,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tech Muchmuche 19:00-21:00; Entrée backstage 23:30-00:30</t>
+          <t>Tech Phusis 18:00-19:30; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Morgana Fargues</t>
+          <t>Morgana</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1114,14 +1110,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tech PCGB 16:00-18:00; Bar public 20:30-22:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Tech PCGB 19:30-20:30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Morgane Scyboz (Lambelet)</t>
+          <t>Morgane</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1129,14 +1125,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
+          <t>Déambule Goulus 16:30-18:00; Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nathalia Koux</t>
+          <t>Nathalia</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1144,14 +1140,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Entrée backstage 19:00-20:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noah Cherpillod</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1159,14 +1155,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Patrick Chambaz</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1177,7 +1173,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rama Assaoui</t>
+          <t>Rama</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1185,29 +1181,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Ailes 16:00-18:00; Déambule FBI 21:30-23:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Raphaël Lacroze</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tech T'es rien… 17:00-19:00</t>
+          <t>Tech T'es rien… 17:00-18:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Raphaëlle Neidhart</t>
+          <t>Raphaëlle</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1215,14 +1211,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Abeilles Ruche 16:00-17:30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Roxanne Lanni</t>
+          <t>Roxanne</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1230,14 +1226,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Simon Lambelet</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1245,14 +1241,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30; Ailes 22:00-24:00</t>
+          <t>Déambule Goulus 20:00-21:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sébastien Schiesser</t>
+          <t>Sébastien</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1263,7 +1259,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Theo Cyprien</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1271,14 +1267,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Déambule Gerry 16:30-18:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Déambule Goulus 16:30-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thibault Clerici</t>
+          <t>Thibault</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1293,7 +1289,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Titouan Ménétrey</t>
+          <t>Titouan</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1301,14 +1297,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
+          <t>Bar loges 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tristan Clerici</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1316,14 +1312,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Yann Bally</t>
+          <t>Yann</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1331,14 +1327,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
+          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ysatis Ménétrey</t>
+          <t>Ysatis</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1346,7 +1342,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Déambule Colbok 17:00-19:00; Ailes 22:00-24:00</t>
+          <t>Bar loges 18:00-19:30; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1433,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Athénaé Marchand, Lucas Chastroux, Morgane Scyboz (Lambelet)</t>
+          <t>Corentin, Morgana, Raphaëlle</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1464,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alexandra Bastian, Jules Pirolley, Thibault Clerici</t>
+          <t>Louis C., Maya C., Thibault</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1495,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emma De Filippo, Léa Baltzinger, Mickaël Pasche</t>
+          <t>Nathalia, Tristan, Yann</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1526,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corentin Meige, Rama Assaoui, Titouan Ménétrey</t>
+          <t>Arthur, Lucas, Titouan</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1557,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jolan Ruscio, Theo Cyprien, Thibault Clerici</t>
+          <t>Thibault, Mireille, Maya R.</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1588,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Marot Ledru</t>
+          <t>Lucie, Maëlan</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1619,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alice L'Horset, Iris Rakotonandrasana, Noah Cherpillod</t>
+          <t>Enzo, Lucas, Rama</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antonin Noël, Louis Cardis, Louis Post</t>
+          <t>Léa B., Marot, Roxanne</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Annouk Malric, Athénaé Marchand, Enzo Maître</t>
+          <t>Agathe, Enzo, Theo</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1712,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Simon Lambelet, Ysatis Ménétrey, Maya Rieger</t>
+          <t>Marot, Roxanne, Ysatis</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1743,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Enzo Maître, Rama Assaoui</t>
+          <t>Louis P., Titouan</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1774,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anna Mallet, Simon Lambelet</t>
+          <t>Lisa J., Ysatis</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1805,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lisa Jaquet, Tristan Clerici</t>
+          <t>Lina-Rosa, Mickaël</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1836,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Agathe Bouvet, Eugénie Prouvost</t>
+          <t>Arsène, Louis P.</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iris Rakotonandrasana, Maëlan Ménétrey</t>
+          <t>Léa C., Raphaël</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1898,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corentin Meige, Roxanne Lanni, Titouan Ménétrey</t>
+          <t>Alice, Athénaé, Lina-Rosa</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1929,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eugénie Prouvost, Jolan Ruscio, Maëlan Ménétrey</t>
+          <t>Anna, Antonin, Jolan</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Léa Chambaz, Lina-Rosa Ledru, Raphaëlle Neidhart, Yann Bally</t>
+          <t>Iris, Léa C., Lucie, Noah</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1991,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alegria Lily Bulka, Arthur Uldry, Morgana Fargues, Roxanne Lanni</t>
+          <t>Analou, Annouk, Corentin, Emma</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2022,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antonin Noël, Louis Post, Morgane Scyboz (Lambelet)</t>
+          <t>Alice, Anna, Jolan</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2053,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Louis Cardis, Lucie Meyer, Yann Bally</t>
+          <t>Louis C., Mickaël, Simon</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2084,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Annouk Malric</t>
+          <t>Annouk</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2115,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mathis Cuinet</t>
+          <t>Auxence</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2146,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nathalia Koux</t>
+          <t>Jules</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2177,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Auxence Magerand</t>
+          <t>Athénaé</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2208,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anna Mallet</t>
+          <t>Antonin</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mireille Ménard</t>
+          <t>Yann</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2270,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Theo Cyprien</t>
+          <t>Arthur</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2301,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arsène Tessier</t>
+          <t>Alegria Lily</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2332,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ysatis Ménétrey</t>
+          <t>Maëlan</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2363,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ava Baruch</t>
+          <t>Ava</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthur Uldry, Auxence Magerand</t>
+          <t>Morgane, Theo</t>
         </is>
       </c>
     </row>
@@ -2429,14 +2425,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Analou Ledru, Marot Ledru</t>
+          <t>Morgane, Simon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie</t>
+          <t>Déambule Volkanik</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2460,24 +2456,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Maya Corbelli</t>
+          <t>Emma</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Déambule Ko-compagnie</t>
+          <t>Déambule Volkanik</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2491,7 +2487,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lucas Chastroux</t>
+          <t>Iris</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2518,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lucie Meyer</t>
+          <t>Alexandra</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2530,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2553,7 +2549,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alice L'Horset</t>
+          <t>Alexandra</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2580,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Maya Rieger</t>
+          <t>Mathis</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2611,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alexandra Bastian</t>
+          <t>Rama</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2642,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mathis Cuinet</t>
+          <t>Mathis</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2654,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2677,7 +2673,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Morgana Fargues</t>
+          <t>Morgana</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2690,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2708,24 +2704,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Raphaël Lacroze</t>
+          <t>Raphaël</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tech Muchmuche</t>
+          <t>Tech Phusis</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2739,7 +2735,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mireille Ménard</t>
+          <t>Mireille</t>
         </is>
       </c>
     </row>

--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ailes 20:00-22:00</t>
+          <t>Bar public 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -479,11 +479,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Déambule Gerry 20:30-22:00</t>
+          <t>Bar public 17:30-19:00; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -494,11 +494,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik 17:00-19:00; Déambule Spoutnik 22:00-23:00</t>
+          <t>Déambule Spoutnik 17:00-19:00</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar public 22:00-23:30</t>
+          <t>Ailes 18:00-20:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bar public 20:30-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
+          <t>Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Entrée backstage 22:00-23:30</t>
+          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bar loges 21:00-22:30</t>
+          <t>Entrée backstage 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Déambule Gerry 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Déambule FBI 17:00-19:00; Bar loges 21:00-22:30</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Entrée backstage 20:30-22:00</t>
+          <t>Déambule Volkanik 16:30-18:30; Entrée backstage 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Entrée backstage 17:30-19:00</t>
+          <t>Déambule Goulus 16:30-18:00</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Déambule Colbok 21:00-23:00</t>
+          <t>Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Déambule Volkanik 16:30-18:30; Bar public 20:30-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
@@ -700,11 +700,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Ailes 20:00-22:00</t>
+          <t>Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Déambule Volkanik 22:30-24:00</t>
+          <t>Bar public 16:00-17:30; Déambule Spoutnik 22:00-23:00</t>
         </is>
       </c>
     </row>
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar public 22:00-23:30</t>
+          <t>Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Entrée backstage 19:00-20:30</t>
+          <t>Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lina-Rosa</t>
+          <t>Lisa J.</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -819,40 +819,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar loges 19:30-21:00</t>
+          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lisa J.</t>
+          <t>Lisa M.</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bar loges 18:00-19:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lisa M.</t>
+          <t>Louis C.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Louis C.</t>
+          <t>Louis P.</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -860,55 +860,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Louis P.</t>
+          <t>Louise</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Bar loges 16:30-18:00; Bar loges 21:00-22:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Louise</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Déambule Colbok 17:00-19:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Léa B.</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -916,55 +916,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
+          <t>Entrée backstage 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Léa B.</t>
+          <t>Léa C.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00</t>
+          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Léa C.</t>
+          <t>Marius</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marius</t>
+          <t>Marot</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marot</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -972,29 +972,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
+          <t>Bar loges 16:30-18:00; Tech Jacquard 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Déambule FBI 17:00-19:00; Tech Jacquard 21:00-23:00</t>
+          <t>Déambule Gerry 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1005,74 +1005,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maya C.</t>
+          <t>Maëlan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00</t>
+          <t>Ailes 16:00-18:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maya R.</t>
+          <t>Maëlle</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 17:30-19:00; Déambule FBI 21:30-23:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maëlan</t>
+          <t>Mickaël</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Déambule Colbok 17:00-19:00; Abeilles Ruche 23:30-00:30</t>
+          <t>Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maëlle</t>
+          <t>Mireille</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tech Phusis 18:00-19:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mickaël</t>
+          <t>Morgana</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1080,14 +1088,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00; Bar public 23:30-00:30</t>
+          <t>Tech PCGB 19:30-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mireille</t>
+          <t>Morgane</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1095,14 +1103,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tech Phusis 18:00-19:30; Abeilles Ruche 22:00-23:30</t>
+          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Morgana</t>
+          <t>Nathalia</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1110,70 +1118,70 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Tech PCGB 19:30-20:30</t>
+          <t>Abeilles Ruche 16:00-17:30; Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Morgane</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Déambule Goulus 20:00-21:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nathalia</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Rama</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Bar loges 18:00-19:30; Déambule Volkanik 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tech T'es rien… 17:00-18:30; Entrée backstage 22:00-23:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rama</t>
+          <t>Raphaëlle</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1181,14 +1189,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Déambule FBI 21:30-23:30</t>
+          <t>Bar public 19:00-20:30; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>Roxanne</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1196,44 +1204,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tech T'es rien… 17:00-18:30; Bar loges 22:30-24:00</t>
+          <t>Bar loges 18:00-19:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Raphaëlle</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30</t>
+          <t>Bar public 16:00-17:30; Déambule Colbok 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Roxanne</t>
+          <t>Sébastien</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1241,25 +1245,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Déambule Goulus 20:00-21:30; Bar public 23:30-00:30</t>
+          <t>Déambule Gerry 16:30-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sébastien</t>
+          <t>Thibault</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Entrée backstage 16:00-17:30; Déambule Goulus 20:00-21:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Titouan</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1267,14 +1275,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Ailes 20:00-22:00</t>
+          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thibault</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1282,14 +1290,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Déambule Goulus 16:30-18:00; Ailes 20:00-22:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Titouan</t>
+          <t>Yann</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1297,52 +1305,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
+          <t>Bar loges 16:30-18:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Ysatis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Yann</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 19:00-20:30; Entrée backstage 23:30-00:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Ysatis</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Bar loges 18:00-19:30; Ailes 22:00-24:00</t>
+          <t>Abeilles Ruche 16:00-17:30; Bar loges 19:30-21:00</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1433,7 +1411,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corentin, Morgana, Raphaëlle</t>
+          <t>Antonin, Nathalia, Ysatis</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1442,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Louis C., Maya C., Thibault</t>
+          <t>Lisa J., Louis C., Louis P.</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1473,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nathalia, Tristan, Yann</t>
+          <t>Analou, Emma, Noah</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1504,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthur, Lucas, Titouan</t>
+          <t>Ava, Jolan, Maya</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1535,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thibault, Mireille, Maya R.</t>
+          <t>Alice, Maëlan, Yann</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lucie, Maëlan</t>
+          <t>Alegria Lily, Emma</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1597,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Enzo, Lucas, Rama</t>
+          <t>Maëlan, Maya, Titouan</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1628,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Léa B., Marot, Roxanne</t>
+          <t>Alice, Léa C., Lucas</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1659,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Agathe, Enzo, Theo</t>
+          <t>Enzo, Mickaël, Tristan</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1690,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marot, Roxanne, Ysatis</t>
+          <t>Léa C., Lisa J., Louis P.</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1721,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Louis P., Titouan</t>
+          <t>Mathis, Yann</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1752,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lisa J., Ysatis</t>
+          <t>Rama, Roxanne</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1783,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lina-Rosa, Mickaël</t>
+          <t>Anna, Ysatis</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1814,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arsène, Louis P.</t>
+          <t>Arthur, Marot</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1845,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Léa C., Raphaël</t>
+          <t>Morgana, Morgane</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1876,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alice, Athénaé, Lina-Rosa</t>
+          <t>Annouk, Iris, Simon</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1907,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anna, Antonin, Jolan</t>
+          <t>Alegria Lily, Maëlle, Marot</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1938,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iris, Léa C., Lucie, Noah</t>
+          <t>Agathe, Corentin, Morgane, Raphaëlle</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1969,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Analou, Annouk, Corentin, Emma</t>
+          <t>Annouk, Jules, Theo, Titouan</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2000,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alice, Anna, Jolan</t>
+          <t>Antonin, Léa B., Lucas</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2031,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Louis C., Mickaël, Simon</t>
+          <t>Corentin, Louis C., Roxanne</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2062,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Annouk</t>
+          <t>Thibault</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2093,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Auxence</t>
+          <t>Léa B.</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2124,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Arsène</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2186,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antonin</t>
+          <t>Raphaël</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2217,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yann</t>
+          <t>Raphaëlle</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2248,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Theo</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2279,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alegria Lily</t>
+          <t>Matteo</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2310,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Maëlan</t>
+          <t>Lucie</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2341,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Simon</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2372,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Morgane, Theo</t>
+          <t>Auxence, Tristan</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2403,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Morgane, Simon</t>
+          <t>Nathalia, Thibault</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2434,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Athénaé</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2465,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Iris</t>
+          <t>Rama</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2527,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Iris</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2558,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Arthur</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2589,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rama</t>
+          <t>Maëlle</t>
         </is>
       </c>
     </row>
@@ -2750,6 +2728,13 @@
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>(***) Personne affectée malgré une préférence de blocage (priorité 3)</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2798,7 +2783,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aucune</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2813,7 +2798,469 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tous les besoins sont couverts et tous les blocages respectés</t>
+          <t>Anna n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Annouk n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enzo n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jolan n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Marot n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mathis n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Maya n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mickaël n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mireille n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Noah n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Titouan n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ysatis n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Alexandra n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Anna n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Auxence n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enzo n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jolan n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lucie n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Matteo n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mickaël n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mireille n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Noah n'a fait que 1 shift(s) sur 2 attendus</t>
         </is>
       </c>
     </row>

--- a/output/planning_Mardi.xlsx
+++ b/output/planning_Mardi.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30</t>
+          <t>Ailes 19:00-20:30</t>
         </is>
       </c>
     </row>
@@ -483,59 +483,59 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Abeilles Ruche 23:30-00:30</t>
+          <t>Déambule Goulus 16:30-18:00; Bar public 20:30-22:00 (**)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik 17:00-19:00</t>
+          <t>Bar loges 19:00-20:30; Entrée backstage 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Bar loges 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analou</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Abeilles Ruche 15:45-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ana-Lou</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -543,14 +543,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bar loges 19:30-21:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Annouk</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -558,14 +558,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Bar public 20:30-22:00</t>
+          <t>Bar public 17:30-19:00; Entrée backstage 22:00-23:30 (**)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antonin</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -573,29 +573,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Bar public 22:00-23:30</t>
+          <t>Ailes 17:30-19:00; Bar public 22:00-23:30 (**)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Annouk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Entrée backstage 19:00-20:30</t>
+          <t>Déambule Gerry 16:30-18:00; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Antonin</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -603,167 +603,175 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Déambule FBI 17:00-19:00; Bar loges 21:00-22:30</t>
+          <t>Déambule Goulus 20:00-21:30; Bar public 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Athénaé</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Déambule Volkanik 16:30-18:30; Entrée backstage 20:30-22:00</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Auxence</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00</t>
+          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Athénaé</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 20:30-22:00</t>
+          <t>Entrée backstage 17:30-19:00; Déambule Colbok 21:00-23:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Benoît</t>
+          <t>Auxence</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Abeilles Ruche 15:45-17:30; Bar loges 20:30-22:00 (***)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Corentin</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Bar public 23:30-00:30</t>
+          <t>Ailes 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Benoît</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Corentin</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ailes 20:00-22:00</t>
+          <t>Ailes 16:00-17:30; Bar public 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Eugénie</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bar loges 17:30-19:00; Bar public 23:30-00:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Iris</t>
+          <t>Eugénie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar public 16:00-17:30; Déambule Spoutnik 22:00-23:00</t>
+          <t>Bar loges 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamilah</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bar public 19:00-20:30; Bar loges 23:30-01:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jolan</t>
+          <t>Iris</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 20:30-22:00</t>
+          <t>Bar public 16:00-17:30; Ailes 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Jamilah</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -774,22 +782,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Jolan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bar public 20:30-22:00</t>
+          <t>Déambule Goulus 16:30-18:00; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -800,33 +808,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kristel</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ailes 19:00-20:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lisa J.</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lisa M.</t>
+          <t>Kristel</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -837,7 +845,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Louis C.</t>
+          <t>Lisa J.</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -845,40 +853,40 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 17:30-19:00; Bar public 23:30-00:30</t>
+          <t>Abeilles Ruche 15:45-17:30; Déambule FBI 21:30-23:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Louis P.</t>
+          <t>Lisa M.</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Louise</t>
+          <t>Louis C.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ailes 16:00-17:30; Déambule Gerry 20:30-22:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Louis P.</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -886,29 +894,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ailes 18:00-20:00; Bar public 22:00-23:30</t>
+          <t>Bar public 16:00-17:30; Entrée backstage 20:30-22:00 (***)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Louise</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Déambule Colbok 17:00-19:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Léa B.</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -916,70 +920,70 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Entrée backstage 17:30-19:00; Bar public 22:00-23:30</t>
+          <t>Bar loges 19:00-20:30; Ailes 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Léa C.</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ailes 18:00-20:00; Ailes 22:00-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marius</t>
+          <t>Léa B.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Déambule FBI 17:00-19:00; Déambule Spoutnik 22:00-23:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marot</t>
+          <t>Léa C.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Bar loges 21:00-22:30</t>
+          <t>Bar public 17:30-19:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Marius</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bar loges 16:30-18:00; Tech Jacquard 21:00-23:00</t>
+          <t>Tech Phusis 18:00-19:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Marot</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -987,55 +991,55 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Déambule Gerry 20:30-22:00</t>
+          <t>Ailes 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Abeilles Ruche 17:30-19:00; Ailes 22:00-23:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ailes 16:00-18:00; Abeilles Ruche 20:30-22:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maëlan</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Abeilles Ruche 22:00-23:30</t>
+          <t>Tech Jacquard 20:15-22:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maëlle</t>
+          <t>Maya C.</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1043,29 +1047,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bar public 17:30-19:00; Déambule FBI 21:30-23:30</t>
+          <t>Déambule Colbok 17:00-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mickaël</t>
+          <t>Maya R.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ailes 20:00-22:00</t>
+          <t>Bar public 17:30-19:00; Abeilles Ruche 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mireille</t>
+          <t>Maëlan</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1073,44 +1077,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tech Phusis 18:00-19:30</t>
+          <t>Abeilles Ruche 19:00-20:30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Morgana</t>
+          <t>Maëlle</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tech PCGB 19:30-20:30; Bar loges 22:30-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Morgane</t>
+          <t>Mehdi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Bar public 19:00-20:30; Bar loges 22:30-24:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nathalia</t>
+          <t>Mickaël</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1118,40 +1114,44 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 16:00-17:30; Déambule Goulus 20:00-21:30</t>
+          <t>Ailes 16:00-17:30; Déambule Goulus 20:00-21:30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Mireille</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Abeilles Ruche 19:00-20:30</t>
+          <t>Ailes 17:30-19:00; Déambule Volkanik 22:30-24:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Morgana</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tech PCGB 19:30-20:30; Ailes 23:30-00:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rama</t>
+          <t>Morgane</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bar loges 18:00-19:30; Déambule Volkanik 22:30-24:00</t>
+          <t>Ailes 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>Nathalia</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1174,14 +1174,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tech T'es rien… 17:00-18:30; Entrée backstage 22:00-23:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Raphaëlle</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1189,55 +1189,51 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bar public 19:00-20:30; Entrée backstage 23:30-00:30</t>
+          <t>Abeilles Ruche 17:30-19:00; Bar public 22:00-23:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Roxanne</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bar loges 18:00-19:30; Bar public 23:30-00:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Rama</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Bar public 16:00-17:30; Déambule Colbok 21:00-23:00</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sébastien</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tech T'es rien… 17:00-18:30; Abeilles Ruche 22:00-23:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Raphaëlle</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1245,14 +1241,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Déambule Gerry 16:30-18:00; Bar public 20:30-22:00</t>
+          <t>Entrée backstage 19:00-20:30; Bar loges 23:30-01:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Thibault</t>
+          <t>Roxanne</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1260,14 +1256,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Entrée backstage 16:00-17:30; Déambule Goulus 20:00-21:30</t>
+          <t>Bar loges 16:00-17:30; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Titouan</t>
+          <t>Sacha</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1275,14 +1271,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ailes 16:00-18:00; Bar public 20:30-22:00</t>
+          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1290,37 +1286,123 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Déambule Goulus 16:30-18:00; Ailes 20:00-22:00</t>
+          <t>Déambule Volkanik 16:30-18:30; Abeilles Ruche 20:30-22:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Yann</t>
+          <t>Sébastien</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Bar loges 16:30-18:00; Abeilles Ruche 22:00-23:30</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Entrée backstage 15:45-17:30; Bar loges 20:30-22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Thibault</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bar public 19:00-20:30; Abeilles Ruche 23:30-00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Tician</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bar public 16:00-17:30; Ailes 20:30-22:00 (***)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Titouan</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ailes 19:00-20:30; Bar public 23:30-00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Tristan</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bar loges 17:30-19:00; Ailes 22:00-23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Yann</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Déambule Spoutnik 17:00-19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Ysatis</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Abeilles Ruche 16:00-17:30; Bar loges 19:30-21:00</t>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bar loges 16:00-17:30; Ailes 23:30-00:30 (***)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1411,7 +1493,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antonin, Nathalia, Ysatis</t>
+          <t>Alice, Auxence, Lisa J.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1524,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lisa J., Louis C., Louis P.</t>
+          <t>Mathis, Nathalia, Noah</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1555,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Analou, Emma, Noah</t>
+          <t>Ana-Lou, Arsène, Maëlan</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1586,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ava, Jolan, Maya</t>
+          <t>Jolan, Roxanne, Simon</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1617,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alice, Maëlan, Yann</t>
+          <t>Maya C., Raphaël, Maya R.</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1638,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alegria Lily, Emma</t>
+          <t>Arthur, Thibault, Sacha</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1665,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1597,7 +1679,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Maëlan, Maya, Titouan</t>
+          <t>Corentin, Louis C., Mickaël</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1691,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1628,7 +1710,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alice, Léa C., Lucas</t>
+          <t>Anna, Mireille, Morgane</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1722,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1659,7 +1741,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Enzo, Mickaël, Tristan</t>
+          <t>Agathe, Jules, Titouan</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1753,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>22:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>24:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1690,69 +1772,69 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Léa C., Lisa J., Louis P.</t>
+          <t>Ava, Iris, Tician (***)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mathis, Yann</t>
+          <t>Marot, Mathis, Tristan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rama, Roxanne</t>
+          <t>Lucas, Morgana, Ysatis (***)</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1846,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1783,7 +1865,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anna, Ysatis</t>
+          <t>Roxanne, Ysatis</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1877,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1814,7 +1896,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthur, Marot</t>
+          <t>Emma, Tristan</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1908,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1845,100 +1927,100 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Morgana, Morgane</t>
+          <t>Lucas, Alex</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Annouk, Iris, Simon</t>
+          <t>Auxence (***), Theo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alegria Lily, Maëlle, Marot</t>
+          <t>Alexandra, Eugénie</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Agathe, Corentin, Morgane, Raphaëlle</t>
+          <t>Raphaëlle, Frank</t>
         </is>
       </c>
     </row>
@@ -1950,26 +2032,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Annouk, Jules, Theo, Titouan</t>
+          <t>Iris, Louis P., Tician</t>
         </is>
       </c>
     </row>
@@ -1981,12 +2063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2000,7 +2082,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antonin, Léa B., Lucas</t>
+          <t>Andy, Léa C., Maya R.</t>
         </is>
       </c>
     </row>
@@ -2012,119 +2094,119 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corentin, Louis C., Roxanne</t>
+          <t>Arthur, Thibault, Frank, Sacha</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thibault</t>
+          <t>Alegria Lily (**), Alice, Annouk, Corentin</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Léa B.</t>
+          <t>Anna (**), Morgane, Nathalia, Noah</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arsène</t>
+          <t>Antonin, Emma, Titouan</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2218,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2155,7 +2237,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Athénaé</t>
+          <t>Theo</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2249,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2186,7 +2268,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>Athénaé</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2280,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2224,17 +2306,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Déambule Gerry</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2248,24 +2330,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Louis P. (***)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Déambule Gerry</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2279,24 +2361,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Andy (**)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Déambule Colbok</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2310,24 +2392,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Alex</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Déambule Colbok</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2341,86 +2423,86 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Annouk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Déambule Goulus</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Auxence, Tristan</t>
+          <t>Louis C.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Déambule Goulus</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nathalia, Thibault</t>
+          <t>Maya C.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Déambule Volkanik</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2441,79 +2523,79 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Déambule Volkanik</t>
+          <t>Déambule Goulus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rama</t>
+          <t>Alegria Lily, Jolan</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik</t>
+          <t>Déambule Goulus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Antonin, Mickaël</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik</t>
+          <t>Déambule Volkanik</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2527,24 +2609,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Iris</t>
+          <t>Simon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Déambule FBI</t>
+          <t>Déambule Volkanik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2558,24 +2640,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Mireille</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Déambule FBI</t>
+          <t>Déambule Spoutnik</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2589,19 +2671,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Maëlle</t>
+          <t>Yann</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tech Jacquard</t>
+          <t>Déambule Spoutnik</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2620,24 +2702,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Léa B.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tech PCGB</t>
+          <t>Déambule FBI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2651,24 +2733,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Morgana</t>
+          <t>Léa B.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tech T'es rien…</t>
+          <t>Déambule FBI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2682,7 +2764,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>Lisa J.</t>
         </is>
       </c>
     </row>
@@ -2713,28 +2795,121 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mireille</t>
+          <t>Marius</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>(**) Personne affectée malgré un blocage de priorité 1</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tech Jacquard</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Maxime</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tech PCGB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Morgana</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>(***) Personne affectée malgré une préférence de blocage (priorité 3)</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tech T'es rien…</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Raphaël</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>(*) Personne affectée malgré un blocage de priorité 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>(**) Personne affectée malgré un blocage de priorité 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>(***) Personne affectée malgré un blocage de priorité 3</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2783,154 +2958,154 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 2)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22:00-23:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anna n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Andy avait indiqué une préférence (priorité 2) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 2)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20:30-22:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Annouk n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Alegria Lily avait indiqué une préférence (priorité 2) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 2)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bar public</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22:00-23:30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enzo n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Anna avait indiqué une préférence (priorité 2) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 3)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20:30-22:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jolan n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Louis P. avait indiqué une préférence (priorité 3) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 3)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bar loges</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20:30-22:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Marot n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Auxence avait indiqué une préférence (priorité 3) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 3)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23:30-00:30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mathis n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Ysatis avait indiqué une préférence (priorité 3) sur ce créneau (Asaf Avidan)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rotation Déambule/tardif manquante</t>
+          <t>Préférence non respectée (priorité 3)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20:30-22:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Maya n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Tician avait indiqué une préférence (priorité 3) sur ce créneau (Lorde)</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3127,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mickaël n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Alice n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3149,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mireille n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Auxence n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3171,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Noah n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Corentin n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3193,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Titouan n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Iris n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
@@ -3040,14 +3215,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ysatis n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+          <t>Julie n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3062,14 +3237,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alexandra n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Léa C. n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3084,14 +3259,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Anna n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Lisa M. n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3106,14 +3281,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Auxence n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Louis P. n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3128,14 +3303,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Enzo n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Maëlan n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3150,14 +3325,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jolan n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Maëlle n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3172,14 +3347,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lucie n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Marius n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3194,14 +3369,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Matteo n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Maxime n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3216,14 +3391,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mickaël n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Roxanne n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shifts incomplets</t>
+          <t>Rotation Déambule/tardif manquante</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3238,29 +3413,95 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mireille n'a fait que 1 shift(s) sur 2 attendus</t>
+          <t>Theo n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tician n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Rotation Déambule/tardif manquante</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mehdi n'a encore eu aucun créneau Déambule ou tardif cette semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Shifts incomplets</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Noah n'a fait que 1 shift(s) sur 2 attendus</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Maëlan n'a fait que 1 shift(s) sur 2 attendus</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shifts incomplets</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Yann n'a fait que 1 shift(s) sur 2 attendus</t>
         </is>
       </c>
     </row>
